--- a/output/graficos_nacionales/plot_nacional_serie_p_basica_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_p_basica_a_2021.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-07 12:22</t>
+    <t xml:space="preserve">2026-09-09 21:10</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_p_basica_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_p_basica_a_2021.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 21:10</t>
+    <t xml:space="preserve">2026-09-18 11:57</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_nacionales/plot_nacional_serie_p_basica_a_2021.xlsx
+++ b/output/graficos_nacionales/plot_nacional_serie_p_basica_a_2021.xlsx
@@ -30,7 +30,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 11:57</t>
+    <t xml:space="preserve">2026-10-05 19:06</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
